--- a/output/pdf_financials_xlsx/WFG.xlsx
+++ b/output/pdf_financials_xlsx/WFG.xlsx
@@ -867,7 +867,7 @@
         <v>115</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>149</v>
@@ -1107,7 +1107,7 @@
         <v>115</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>149</v>
@@ -1268,10 +1268,10 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -6727,7 +6727,7 @@
         <v>199</v>
       </c>
       <c r="U77" s="3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V77" s="1" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>199</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="V79" s="1" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>0.06908486778346948</v>
       </c>
       <c r="U80" s="3" t="n">
-        <v>0.05752085130859937</v>
+        <v>0.02876042565429968</v>
       </c>
       <c r="V80" s="1" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -82409,7 +82409,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
@@ -86854,7 +86854,7 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -88417,7 +88417,7 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
@@ -88665,7 +88665,7 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">
@@ -90347,7 +90347,7 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
